--- a/Result/profitability/4585.xlsx
+++ b/Result/profitability/4585.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM18"/>
+  <dimension ref="A1:AM19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2716,6 +2716,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>4585</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>512</v>
+      </c>
+      <c r="D19" t="n">
+        <v>244</v>
+      </c>
+      <c r="E19" t="n">
+        <v>268</v>
+      </c>
+      <c r="F19" t="n">
+        <v>52.27</v>
+      </c>
+      <c r="G19" t="n">
+        <v>41</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>7.95%</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>97</v>
+      </c>
+      <c r="J19" t="n">
+        <v>138</v>
+      </c>
+      <c r="K19" t="n">
+        <v>123</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.48125</v>
+      </c>
+      <c r="N19" t="n">
+        <v>51.96625</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.5299999999999999</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.8153846153846152</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.390000000000001</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.04791499599037685</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-4.575757575757575</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.3400000000000034</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.006547275178124368</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK19" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
